--- a/servers/maze_main_server/conf.d/data/maze_save_monsters_v8【迷宫-救援敌人】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_save_monsters_v8【迷宫-救援敌人】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C3BD0DC-E281-4AE9-9ED3-E81A0DD7560C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D51B4F1-DE23-4237-ABD1-333074F8C16D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/servers/maze_main_server/conf.d/data/maze_save_monsters_v8【迷宫-救援敌人】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_save_monsters_v8【迷宫-救援敌人】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D51B4F1-DE23-4237-ABD1-333074F8C16D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50080E65-4549-495F-AD4E-6C9402EDDF04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="18">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -53,9 +53,6 @@
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>STRING_C_S</t>
   </si>
   <si>
     <t>name</t>
@@ -504,13 +501,13 @@
         <v>2</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.15">
@@ -518,33 +515,33 @@
         <v>3</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="C4" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
@@ -552,7 +549,7 @@
         <v>1</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C5" s="1">
         <v>800001011</v>
@@ -569,7 +566,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C6" s="1">
         <v>800004011</v>
@@ -586,7 +583,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C7" s="1">
         <v>800001021</v>
@@ -603,7 +600,7 @@
         <v>4</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C8" s="1">
         <v>800001031</v>

--- a/servers/maze_main_server/conf.d/data/maze_save_monsters_v8【迷宫-救援敌人】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_save_monsters_v8【迷宫-救援敌人】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50080E65-4549-495F-AD4E-6C9402EDDF04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0637D198-2058-49A4-BCF8-962834EDD1A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_save_monsters_v8" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="17">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -91,17 +91,15 @@
     <t>骷髅1</t>
   </si>
   <si>
-    <t>狼1</t>
-  </si>
-  <si>
-    <t>骷髅2</t>
-  </si>
-  <si>
-    <t>骷髅3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>移速</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>僵尸1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>僵尸2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -538,7 +536,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>12</v>
@@ -555,7 +553,7 @@
         <v>800001011</v>
       </c>
       <c r="D5" s="1">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="E5" s="1">
         <v>20</v>
@@ -566,13 +564,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C6" s="1">
-        <v>800004011</v>
+        <v>800003011</v>
       </c>
       <c r="D6" s="1">
-        <v>450</v>
+        <v>300</v>
       </c>
       <c r="E6" s="1">
         <v>40</v>
@@ -583,16 +581,16 @@
         <v>3</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C7" s="1">
-        <v>800001021</v>
+        <v>800003021</v>
       </c>
       <c r="D7" s="1">
         <v>300</v>
       </c>
       <c r="E7" s="1">
-        <v>60</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.15">
@@ -603,13 +601,13 @@
         <v>16</v>
       </c>
       <c r="C8" s="1">
-        <v>800001031</v>
+        <v>800003021</v>
       </c>
       <c r="D8" s="1">
         <v>300</v>
       </c>
       <c r="E8" s="1">
-        <v>100</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>

--- a/servers/maze_main_server/conf.d/data/maze_save_monsters_v8【迷宫-救援敌人】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_save_monsters_v8【迷宫-救援敌人】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0637D198-2058-49A4-BCF8-962834EDD1A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{533C57CD-BD0B-484F-A5AE-BD088000EB5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -95,11 +95,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>僵尸1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>僵尸2</t>
+    <t>强盗1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>骷髅3</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -567,7 +567,7 @@
         <v>15</v>
       </c>
       <c r="C6" s="1">
-        <v>800003011</v>
+        <v>800002011</v>
       </c>
       <c r="D6" s="1">
         <v>300</v>
@@ -584,7 +584,7 @@
         <v>16</v>
       </c>
       <c r="C7" s="1">
-        <v>800003021</v>
+        <v>800001031</v>
       </c>
       <c r="D7" s="1">
         <v>300</v>
@@ -601,7 +601,7 @@
         <v>16</v>
       </c>
       <c r="C8" s="1">
-        <v>800003021</v>
+        <v>800001031</v>
       </c>
       <c r="D8" s="1">
         <v>300</v>

--- a/servers/maze_main_server/conf.d/data/maze_save_monsters_v8【迷宫-救援敌人】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_save_monsters_v8【迷宫-救援敌人】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{533C57CD-BD0B-484F-A5AE-BD088000EB5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAF429D2-CB22-4059-B6BA-B954205EEE75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_save_monsters_v8" sheetId="1" r:id="rId1"/>
@@ -573,7 +573,7 @@
         <v>300</v>
       </c>
       <c r="E6" s="1">
-        <v>40</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.15">
@@ -590,7 +590,7 @@
         <v>300</v>
       </c>
       <c r="E7" s="1">
-        <v>80</v>
+        <v>90</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.15">
@@ -607,7 +607,7 @@
         <v>300</v>
       </c>
       <c r="E8" s="1">
-        <v>80</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
